--- a/data/trans_orig/P1428-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2007</t>
+          <t>Población con diagnóstico de artritis en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>856</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485219</t>
+          <t>485042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492998</t>
+          <t>493208</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>460847</t>
+          <t>461754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950642</t>
+          <t>950174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959654</t>
+          <t>959615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>19530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725693</t>
+          <t>726785</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734471</t>
+          <t>734474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608390</t>
+          <t>609023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>622317</t>
+          <t>621971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1340950</t>
+          <t>1341452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355569</t>
+          <t>1355301</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>9126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53439</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31992</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56325</t>
+          <t>55894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>628694</t>
+          <t>629542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637554</t>
+          <t>637566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636305</t>
+          <t>637242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660944</t>
+          <t>661853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272087</t>
+          <t>1272518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1296420</t>
+          <t>1297299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37754</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60630</t>
+          <t>61004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91219</t>
+          <t>93043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82259</t>
+          <t>83178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>123687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>481393</t>
+          <t>481963</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>502613</t>
+          <t>502092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424423</t>
+          <t>422599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455012</t>
+          <t>454638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>913332</t>
+          <t>911102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>952530</t>
+          <t>951611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>49400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78998</t>
+          <t>79659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96611</t>
+          <t>94435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131884</t>
+          <t>130397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155419</t>
+          <t>153037</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201187</t>
+          <t>201263</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307712</t>
+          <t>307051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>336141</t>
+          <t>337310</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>272102</t>
+          <t>273589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>307375</t>
+          <t>309551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589509</t>
+          <t>589433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>635277</t>
+          <t>637659</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>50908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78409</t>
+          <t>78066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>145636</t>
+          <t>142654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180283</t>
+          <t>178411</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202427</t>
+          <t>204594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>249184</t>
+          <t>247507</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214174</t>
+          <t>214517</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240712</t>
+          <t>241675</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162651</t>
+          <t>164523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>197298</t>
+          <t>200280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>386333</t>
+          <t>388010</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>433090</t>
+          <t>430923</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59366</t>
+          <t>60322</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85588</t>
+          <t>86761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178628</t>
+          <t>178486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>218427</t>
+          <t>217779</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249128</t>
+          <t>246019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295449</t>
+          <t>294001</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124295</t>
+          <t>123122</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>150517</t>
+          <t>149561</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115481</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155280</t>
+          <t>155422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248342</t>
+          <t>249790</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>294663</t>
+          <t>297772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>208868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>266808</t>
+          <t>267097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>554495</t>
+          <t>552263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>643555</t>
+          <t>640890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>775323</t>
+          <t>777516</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>886437</t>
+          <t>889127</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3009735</t>
+          <t>3009446</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3068221</t>
+          <t>3067675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2735642</t>
+          <t>2738307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2824702</t>
+          <t>2826934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5769304</t>
+          <t>5766614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5880418</t>
+          <t>5878225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2012</t>
+          <t>Población con diagnóstico de artritis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449547</t>
+          <t>450461</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423116</t>
+          <t>421576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875665</t>
+          <t>876128</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883462</t>
+          <t>883470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18365</t>
+          <t>16758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>21601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>668722</t>
+          <t>670329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>683261</t>
+          <t>684084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>601499</t>
+          <t>600882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609279</t>
+          <t>609283</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1275448</t>
+          <t>1275741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1291317</t>
+          <t>1291473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7915</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23014</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12897</t>
+          <t>13622</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30874</t>
+          <t>31785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667724</t>
+          <t>667582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678942</t>
+          <t>679040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>686560</t>
+          <t>686685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701659</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1360563</t>
+          <t>1359652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1378540</t>
+          <t>1377815</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65606</t>
+          <t>63592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43719</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76103</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593565</t>
+          <t>593741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609235</t>
+          <t>609192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>548658</t>
+          <t>550672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578093</t>
+          <t>578174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1152777</t>
+          <t>1150803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1185161</t>
+          <t>1183583</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>54861</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74137</t>
+          <t>73868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110493</t>
+          <t>107780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108160</t>
+          <t>109376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152339</t>
+          <t>152344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375728</t>
+          <t>374568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>401085</t>
+          <t>399942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>337307</t>
+          <t>340020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373663</t>
+          <t>373932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>724890</t>
+          <t>724885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>769069</t>
+          <t>767853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38002</t>
+          <t>37919</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65487</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99786</t>
+          <t>99603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135983</t>
+          <t>135828</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144075</t>
+          <t>143100</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189435</t>
+          <t>191143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244299</t>
+          <t>242039</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271784</t>
+          <t>271867</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218013</t>
+          <t>218168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254210</t>
+          <t>254393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474347</t>
+          <t>472639</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>519707</t>
+          <t>520682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>73213</t>
+          <t>71516</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146764</t>
+          <t>146701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187133</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>200975</t>
+          <t>197790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>249140</t>
+          <t>247209</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>176638</t>
+          <t>178335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203917</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201846</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242215</t>
+          <t>242278</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>389690</t>
+          <t>391621</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437855</t>
+          <t>441040</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>69,04%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>150414</t>
+          <t>151392</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>205192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>401480</t>
+          <t>398302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>486526</t>
+          <t>480345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>566335</t>
+          <t>569815</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>662678</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3220647</t>
+          <t>3221587</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3276365</t>
+          <t>3275387</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3068572</t>
+          <t>3074753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3153618</t>
+          <t>3156796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6319199</t>
+          <t>6313537</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6415542</t>
+          <t>6412062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2016</t>
+          <t>Población con diagnóstico de artritis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,97 +6691,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5680</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1878</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6571</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5671</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5653</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389184</t>
+          <t>390075</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809565</t>
+          <t>809547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7391</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583205</t>
+          <t>583409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556153</t>
+          <t>553891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1142896</t>
+          <t>1143014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152978</t>
+          <t>1152983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654179</t>
+          <t>654876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666173</t>
+          <t>666167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645465</t>
+          <t>644863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657556</t>
+          <t>657640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303900</t>
+          <t>1304590</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321309</t>
+          <t>1321495</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>30377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57530</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52206</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85016</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609558</t>
+          <t>608618</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>630742</t>
+          <t>629542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591547</t>
+          <t>592374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>617909</t>
+          <t>618700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210109</t>
+          <t>1209141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242919</t>
+          <t>1242850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>35815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99923</t>
+          <t>99581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86016</t>
+          <t>86464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128408</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>440824</t>
+          <t>442103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462115</t>
+          <t>462247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>396926</t>
+          <t>397268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>432762</t>
+          <t>431888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846359</t>
+          <t>848427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>888751</t>
+          <t>888303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76657</t>
+          <t>78970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110437</t>
+          <t>111100</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98550</t>
+          <t>98268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138331</t>
+          <t>138628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298861</t>
+          <t>298427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318376</t>
+          <t>318467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267325</t>
+          <t>266662</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>301105</t>
+          <t>298792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573761</t>
+          <t>573464</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613542</t>
+          <t>613824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28763</t>
+          <t>30094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>51334</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>84142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124450</t>
+          <t>122708</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120001</t>
+          <t>120593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164925</t>
+          <t>163621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>206906</t>
+          <t>205664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>228235</t>
+          <t>226904</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>275719</t>
+          <t>277461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315515</t>
+          <t>316027</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>492242</t>
+          <t>493546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>537166</t>
+          <t>536574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>101492</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142343</t>
+          <t>146115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294992</t>
+          <t>296250</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>369623</t>
+          <t>370515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>411559</t>
+          <t>408237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>500100</t>
+          <t>496976</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3252007</t>
+          <t>3248235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3294562</t>
+          <t>3292858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3174919</t>
+          <t>3174027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3249550</t>
+          <t>3248292</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6438792</t>
+          <t>6441916</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6527333</t>
+          <t>6530655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de artritis en 2023</t>
+          <t>Población con diagnóstico de artritis en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293607</t>
+          <t>294512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311614</t>
+          <t>311613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692956</t>
+          <t>692229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711550</t>
+          <t>711583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499755</t>
+          <t>498871</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510164</t>
+          <t>509764</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923070</t>
+          <t>922815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933099</t>
+          <t>933066</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>22508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14604</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>30873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521987</t>
+          <t>521867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532615</t>
+          <t>532824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518774</t>
+          <t>518520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531164</t>
+          <t>530920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1044862</t>
+          <t>1045171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1061440</t>
+          <t>1061363</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42814</t>
+          <t>43140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48373</t>
+          <t>49425</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80308</t>
+          <t>81906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>54930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114871</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842811</t>
+          <t>842485</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874880</t>
+          <t>875372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625498</t>
+          <t>623900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>657433</t>
+          <t>656381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1476560</t>
+          <t>1476968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1536079</t>
+          <t>1536501</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33569</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58602</t>
+          <t>56550</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87236</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114533</t>
+          <t>113824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127024</t>
+          <t>126713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161551</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500657</t>
+          <t>502709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>525690</t>
+          <t>526416</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428030</t>
+          <t>428739</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>455327</t>
+          <t>454699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940270</t>
+          <t>939011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>974797</t>
+          <t>975108</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>29635</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>48406</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>175470</t>
+          <t>175910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>489672</t>
+          <t>494866</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194546</t>
+          <t>194559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>647545</t>
+          <t>663497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318725</t>
+          <t>318167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336673</t>
+          <t>336938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>112312</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>431708</t>
+          <t>431268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326206</t>
+          <t>310254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>779205</t>
+          <t>779192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71347</t>
+          <t>71703</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>167204</t>
+          <t>168258</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195524</t>
+          <t>196774</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>223792</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>259445</t>
+          <t>260380</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210580</t>
+          <t>210224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233361</t>
+          <t>232471</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228810</t>
+          <t>227560</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257130</t>
+          <t>256076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>446816</t>
+          <t>445881</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482469</t>
+          <t>482298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>136351</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199119</t>
+          <t>202713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>510725</t>
+          <t>508592</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1273082</t>
+          <t>1323440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>663265</t>
+          <t>661515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1509503</t>
+          <t>1704021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3252815</t>
+          <t>3249221</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3313828</t>
+          <t>3315583</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2372529</t>
+          <t>2322171</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3134886</t>
+          <t>3137019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5588043</t>
+          <t>5393525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6434281</t>
+          <t>6436031</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1428-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1428-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485042</t>
+          <t>485008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493208</t>
+          <t>493203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461754</t>
+          <t>460769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950174</t>
+          <t>949794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>959615</t>
+          <t>959210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16471</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>726785</t>
+          <t>727062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734474</t>
+          <t>734480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>609023</t>
+          <t>608699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>621971</t>
+          <t>622350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1341452</t>
+          <t>1341543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355301</t>
+          <t>1355845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27891</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52502</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31113</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55894</t>
+          <t>56454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>629542</t>
+          <t>628951</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637566</t>
+          <t>637539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637242</t>
+          <t>637416</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661853</t>
+          <t>661341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1272518</t>
+          <t>1271958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1297299</t>
+          <t>1296570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37184</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61004</t>
+          <t>59338</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93043</t>
+          <t>90868</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83178</t>
+          <t>82895</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123687</t>
+          <t>122230</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>481963</t>
+          <t>482049</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>502092</t>
+          <t>502586</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>422599</t>
+          <t>424774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>454638</t>
+          <t>456304</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>911102</t>
+          <t>912559</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>951611</t>
+          <t>951894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49400</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79659</t>
+          <t>78839</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94435</t>
+          <t>96165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>130397</t>
+          <t>131381</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>153037</t>
+          <t>154328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>201263</t>
+          <t>201836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307051</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337310</t>
+          <t>337071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>273589</t>
+          <t>272605</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309551</t>
+          <t>307821</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>589433</t>
+          <t>588860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>637659</t>
+          <t>636368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50908</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78066</t>
+          <t>77892</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>142654</t>
+          <t>143933</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178411</t>
+          <t>177656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>204594</t>
+          <t>203789</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>247507</t>
+          <t>249440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>214517</t>
+          <t>214691</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241675</t>
+          <t>240723</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>164523</t>
+          <t>165278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>200280</t>
+          <t>199001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388010</t>
+          <t>386077</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430923</t>
+          <t>431728</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60322</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86761</t>
+          <t>86689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>178486</t>
+          <t>178872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>217779</t>
+          <t>216767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>246019</t>
+          <t>246896</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>294001</t>
+          <t>296389</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>123122</t>
+          <t>123194</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>149561</t>
+          <t>148743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116129</t>
+          <t>117141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>155422</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>249790</t>
+          <t>247402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297772</t>
+          <t>296895</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>208868</t>
+          <t>211644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>267097</t>
+          <t>267642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>552263</t>
+          <t>553969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>640890</t>
+          <t>642144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>777516</t>
+          <t>778081</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>889127</t>
+          <t>889635</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3009446</t>
+          <t>3008901</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3067675</t>
+          <t>3064899</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2738307</t>
+          <t>2737053</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2826934</t>
+          <t>2825228</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5766614</t>
+          <t>5766106</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5878225</t>
+          <t>5877660</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8654</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>9470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450461</t>
+          <t>449949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421576</t>
+          <t>422541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876128</t>
+          <t>874906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883470</t>
+          <t>883466</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16758</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>8727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>670329</t>
+          <t>668559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>684084</t>
+          <t>684035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>600882</t>
+          <t>601528</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>609283</t>
+          <t>609288</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1275741</t>
+          <t>1276303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1291473</t>
+          <t>1291430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22889</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31785</t>
+          <t>30868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667582</t>
+          <t>668778</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679040</t>
+          <t>679059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>686685</t>
+          <t>687072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>701841</t>
+          <t>701960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1359652</t>
+          <t>1360569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1377815</t>
+          <t>1378693</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36090</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63592</t>
+          <t>62961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>44641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>78212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593741</t>
+          <t>594066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609192</t>
+          <t>608378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550672</t>
+          <t>551303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>578174</t>
+          <t>579099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1150803</t>
+          <t>1150668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1183583</t>
+          <t>1184239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73868</t>
+          <t>73626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107780</t>
+          <t>108752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109376</t>
+          <t>110149</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152344</t>
+          <t>156826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374568</t>
+          <t>376077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>399942</t>
+          <t>401101</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340020</t>
+          <t>339048</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373932</t>
+          <t>374174</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>724885</t>
+          <t>720403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>767853</t>
+          <t>767080</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37919</t>
+          <t>37320</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67747</t>
+          <t>66232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>99603</t>
+          <t>96657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>135828</t>
+          <t>132457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>143100</t>
+          <t>145416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>191143</t>
+          <t>189024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>242039</t>
+          <t>243554</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>271867</t>
+          <t>272466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>218168</t>
+          <t>221539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254393</t>
+          <t>257339</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>472639</t>
+          <t>474758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>520682</t>
+          <t>518366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71516</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>146701</t>
+          <t>146015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>185909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>197790</t>
+          <t>198112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247209</t>
+          <t>250176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178335</t>
+          <t>177604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205530</t>
+          <t>203832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201539</t>
+          <t>203070</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242278</t>
+          <t>242964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>391621</t>
+          <t>388654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>441040</t>
+          <t>440718</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151392</t>
+          <t>150975</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205192</t>
+          <t>206819</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>398302</t>
+          <t>401719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>480345</t>
+          <t>481574</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>569815</t>
+          <t>572809</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>668340</t>
+          <t>671632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3221587</t>
+          <t>3219960</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3275387</t>
+          <t>3275804</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3074753</t>
+          <t>3073524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3156796</t>
+          <t>3153379</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6313537</t>
+          <t>6310245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6412062</t>
+          <t>6409068</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5680</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390075</t>
+          <t>390079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809547</t>
+          <t>809553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9653</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583409</t>
+          <t>584277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553891</t>
+          <t>554227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143014</t>
+          <t>1142469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152983</t>
+          <t>1152981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25893</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>654876</t>
+          <t>653427</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666167</t>
+          <t>666117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644863</t>
+          <t>645187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657640</t>
+          <t>657705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1304590</t>
+          <t>1303083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321495</t>
+          <t>1320835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30377</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56703</t>
+          <t>57347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>51044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85984</t>
+          <t>85290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608618</t>
+          <t>609411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629542</t>
+          <t>630472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592374</t>
+          <t>591730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>618700</t>
+          <t>617827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1209141</t>
+          <t>1209835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1242850</t>
+          <t>1244081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15671</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35815</t>
+          <t>36662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64961</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99581</t>
+          <t>97660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>86464</t>
+          <t>85279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>442103</t>
+          <t>441256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462247</t>
+          <t>462704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>397268</t>
+          <t>399189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>431888</t>
+          <t>433183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848427</t>
+          <t>850368</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>888303</t>
+          <t>889488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35903</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>78970</t>
+          <t>77894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111100</t>
+          <t>111085</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>97609</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138628</t>
+          <t>138784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298427</t>
+          <t>299055</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>318467</t>
+          <t>318481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>266662</t>
+          <t>266677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>298792</t>
+          <t>299868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8574,7 +8574,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>573464</t>
+          <t>573308</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613824</t>
+          <t>614483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30094</t>
+          <t>29811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51334</t>
+          <t>49422</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84142</t>
+          <t>84294</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122708</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120593</t>
+          <t>121208</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>163621</t>
+          <t>166351</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205664</t>
+          <t>207576</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>226904</t>
+          <t>227187</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>277461</t>
+          <t>276869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>316027</t>
+          <t>315875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>493546</t>
+          <t>490816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>536574</t>
+          <t>535959</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>101492</t>
+          <t>100603</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>146115</t>
+          <t>145592</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>296250</t>
+          <t>298270</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>370515</t>
+          <t>371859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>408237</t>
+          <t>412329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>496976</t>
+          <t>494081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3248235</t>
+          <t>3248758</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3292858</t>
+          <t>3293747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3174027</t>
+          <t>3172683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3248292</t>
+          <t>3246272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6441916</t>
+          <t>6444811</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6530655</t>
+          <t>6526563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>354668</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294512</t>
+          <t>340526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311613</t>
+          <t>360471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>706187</t>
+          <t>762461</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692229</t>
+          <t>746971</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711583</t>
+          <t>768279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506184</t>
+          <t>494954</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498871</t>
+          <t>488735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509764</t>
+          <t>498743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>929731</t>
+          <t>971844</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922815</t>
+          <t>965740</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>933066</t>
+          <t>975767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15314</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>11031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22508</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,17 +10421,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>24607</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30873</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529016</t>
+          <t>612568</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521867</t>
+          <t>605407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>532824</t>
+          <t>616967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>525714</t>
+          <t>602983</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>518520</t>
+          <t>595436</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>530920</t>
+          <t>609689</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,17 +10534,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1054729</t>
+          <t>1215551</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1045171</t>
+          <t>1205206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1061363</t>
+          <t>1223132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>535017</t>
+          <t>619438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541028</t>
+          <t>620720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1076044</t>
+          <t>1240158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>26615</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43140</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62229</t>
+          <t>62270</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49425</t>
+          <t>51352</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81906</t>
+          <t>74786</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>88633</t>
+          <t>88885</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54930</t>
+          <t>73861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>105667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>859221</t>
+          <t>671807</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>842485</t>
+          <t>659337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875372</t>
+          <t>680647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>643577</t>
+          <t>666928</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>623900</t>
+          <t>654412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>656381</t>
+          <t>677846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1502798</t>
+          <t>1338735</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1476968</t>
+          <t>1321953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1536501</t>
+          <t>1353759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>885625</t>
+          <t>698422</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>885625</t>
+          <t>698422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>885625</t>
+          <t>698422</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>705806</t>
+          <t>729198</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>705806</t>
+          <t>729198</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>705806</t>
+          <t>729198</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1591431</t>
+          <t>1427620</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1591431</t>
+          <t>1427620</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1591431</t>
+          <t>1427620</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>43763</t>
+          <t>45117</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>34572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56550</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100330</t>
+          <t>110249</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>87864</t>
+          <t>95777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113824</t>
+          <t>124523</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>144093</t>
+          <t>155366</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126713</t>
+          <t>137467</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162810</t>
+          <t>174869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>515496</t>
+          <t>562292</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502709</t>
+          <t>547566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526416</t>
+          <t>572837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>442233</t>
+          <t>493715</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428739</t>
+          <t>479441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454699</t>
+          <t>508187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>957728</t>
+          <t>1056008</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>939011</t>
+          <t>1036505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>975108</t>
+          <t>1073907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>559259</t>
+          <t>607409</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>559259</t>
+          <t>607409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>559259</t>
+          <t>607409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>542563</t>
+          <t>603964</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>542563</t>
+          <t>603964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>542563</t>
+          <t>603964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1101821</t>
+          <t>1211374</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1101821</t>
+          <t>1211374</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1101821</t>
+          <t>1211374</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29635</t>
+          <t>32138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48406</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>325158</t>
+          <t>132410</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>175910</t>
+          <t>120096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>494866</t>
+          <t>148098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>363533</t>
+          <t>174050</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194559</t>
+          <t>156993</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>663497</t>
+          <t>191965</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328198</t>
+          <t>363516</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>318167</t>
+          <t>353236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>336938</t>
+          <t>373018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>282020</t>
+          <t>305453</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112312</t>
+          <t>289765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>431268</t>
+          <t>317767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>610218</t>
+          <t>668968</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>310254</t>
+          <t>651053</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>779192</t>
+          <t>686025</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>366573</t>
+          <t>405156</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>366573</t>
+          <t>405156</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366573</t>
+          <t>405156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607178</t>
+          <t>437863</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607178</t>
+          <t>437863</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607178</t>
+          <t>437863</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>973751</t>
+          <t>843018</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>973751</t>
+          <t>843018</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973751</t>
+          <t>843018</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>64865</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>53883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71703</t>
+          <t>76983</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>181840</t>
+          <t>198128</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168258</t>
+          <t>183164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196774</t>
+          <t>213657</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>240862</t>
+          <t>262993</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>223963</t>
+          <t>242468</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>260380</t>
+          <t>284186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>222905</t>
+          <t>244417</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210224</t>
+          <t>232299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232471</t>
+          <t>255399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>242494</t>
+          <t>264841</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>227560</t>
+          <t>249312</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256076</t>
+          <t>279805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>465399</t>
+          <t>509258</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>445881</t>
+          <t>488065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482298</t>
+          <t>529783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281927</t>
+          <t>309282</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281927</t>
+          <t>309282</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281927</t>
+          <t>309282</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424334</t>
+          <t>462969</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424334</t>
+          <t>462969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424334</t>
+          <t>462969</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>772251</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>772251</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>706261</t>
+          <t>772251</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>173564</t>
+          <t>185107</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>160410</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202713</t>
+          <t>210735</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>697191</t>
+          <t>534768</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>508592</t>
+          <t>500818</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1323440</t>
+          <t>566276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>870755</t>
+          <t>719874</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>661515</t>
+          <t>673935</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1704021</t>
+          <t>757593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3278370</t>
+          <t>3339283</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3249221</t>
+          <t>3313655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3315583</t>
+          <t>3363980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2948420</t>
+          <t>3183542</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2322171</t>
+          <t>3152034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3137019</t>
+          <t>3217492</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6226791</t>
+          <t>6522826</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5393525</t>
+          <t>6485107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6436031</t>
+          <t>6568765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451934</t>
+          <t>3524390</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3645611</t>
+          <t>3718310</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7097546</t>
+          <t>7242700</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
